--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98209</v>
+        <v>98215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98215</v>
+        <v>98217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98382</v>
+        <v>98383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98217</v>
+        <v>98218</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98412</v>
+        <v>98413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98383</v>
+        <v>98389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98413</v>
+        <v>98419</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98389</v>
+        <v>98393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>98228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98419</v>
+        <v>98423</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98423</v>
+        <v>98425</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98395</v>
+        <v>98397</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98425</v>
+        <v>98427</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136938187</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>136938694</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>136939006</v>
       </c>
       <c r="B10" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98397</v>
+        <v>98410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98427</v>
+        <v>98440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>136938187</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>136938694</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>136939006</v>
       </c>
       <c r="B10" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98440</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -718,11 +718,7 @@
           <t>kapslar</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -1008,11 +1004,7 @@
           <t>dm²</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1124,11 +1116,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1548,11 +1536,7 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1676,11 +1660,7 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1828,11 +1808,7 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -2072,11 +2048,7 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2199,11 +2171,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98412</v>
+        <v>98415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98247</v>
+        <v>98250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136938187</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136938694</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136939006</v>
       </c>
       <c r="B10" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98415</v>
+        <v>98425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98250</v>
+        <v>98260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98445</v>
+        <v>98455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98260</v>
+        <v>98261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136938187</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136938694</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136939006</v>
       </c>
       <c r="B10" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98426</v>
+        <v>98431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98261</v>
+        <v>98266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98431</v>
+        <v>98433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98266</v>
+        <v>98268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98461</v>
+        <v>98463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136938187</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136938694</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136939006</v>
       </c>
       <c r="B10" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98433</v>
+        <v>98439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98268</v>
+        <v>98274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98463</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98439</v>
+        <v>98451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98274</v>
+        <v>98286</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98451</v>
+        <v>98452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98286</v>
+        <v>98287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98452</v>
+        <v>98455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98287</v>
+        <v>98290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98482</v>
+        <v>98485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92985</v>
+        <v>92986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96649</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106588</v>
+        <v>106590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106622</v>
+        <v>106624</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106622</v>
+        <v>106624</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104161</v>
+        <v>104162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98485</v>
+        <v>98486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 35172-2026 artfynd.xlsx
+++ b/artfynd/A 35172-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136939043</v>
       </c>
       <c r="B2" t="n">
-        <v>96866</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>136938874</v>
       </c>
       <c r="B3" t="n">
-        <v>92986</v>
+        <v>92989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>136940147</v>
       </c>
       <c r="B4" t="n">
-        <v>96650</v>
+        <v>96653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>136940649</v>
       </c>
       <c r="B5" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136938609</v>
       </c>
       <c r="B6" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136938919</v>
       </c>
       <c r="B7" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136938187</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136938694</v>
       </c>
       <c r="B9" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136939006</v>
       </c>
       <c r="B10" t="n">
-        <v>58310</v>
+        <v>58313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136938891</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>136938753</v>
       </c>
       <c r="B12" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>136940163</v>
       </c>
       <c r="B13" t="n">
-        <v>106590</v>
+        <v>106594</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136938306</v>
       </c>
       <c r="B14" t="n">
-        <v>106624</v>
+        <v>106628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136940114</v>
       </c>
       <c r="B15" t="n">
-        <v>106624</v>
+        <v>106628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136938951</v>
       </c>
       <c r="B16" t="n">
-        <v>98291</v>
+        <v>98294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136938333</v>
       </c>
       <c r="B17" t="n">
-        <v>104162</v>
+        <v>104166</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136938334</v>
       </c>
       <c r="B18" t="n">
-        <v>98486</v>
+        <v>98489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
